--- a/examples/include_section_template.xlsx
+++ b/examples/include_section_template.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -602,67 +602,129 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{# enddefine_section #}</t>
+          <t>{% for item in order.items %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - {{ item.name }}</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{{ item.qty }}개</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>{{ item.price }}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{# define_section:일반_주문 #}</t>
+          <t>{% endfor %}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>주문 #{{ order.id }}</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{{ order.customer }}</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>{{ order.amount }}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>{# enddefine_section #}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>{# define_section:일반_주문 #}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>{# define_section:푸터 #}</t>
+          <t>주문 #{{ order.id }}</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{{ order.customer }}</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>{{ order.amount }}</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{% for item in order.items %}</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>총 {{ orders|length }}건의 주문</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - {{ item.name }}</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{{ item.qty }}개</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>{{ item.price }}</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>문의: {{ contact_email }}</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{% endfor %}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>{# enddefine_section #}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>{# define_section:푸터 #}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>총 {{ orders|length }}건의 주문</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>문의: {{ contact_email }}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>{# enddefine_section #}</t>
         </is>

--- a/examples/include_section_template.xlsx
+++ b/examples/include_section_template.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -522,6 +522,34 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>{% include_section "컴포넌트" "푸터" %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{% include_section "없는시트" "헤더" %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>{% include_section "컴포넌트" "없는섹션" %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>{% include_section 없는변수 "헤더" %}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>{% include_section target_sheet "헤더" %}</t>
         </is>
       </c>
     </row>
